--- a/data/output/evaluation/openai/internal-consistency/all-criteria/rank_stability.xlsx
+++ b/data/output/evaluation/openai/internal-consistency/all-criteria/rank_stability.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,13 +460,13 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7071067811865476</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -476,10 +476,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4216370213557839</v>
+        <v>0.816496580927726</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9660917830792959</v>
+        <v>1.418136492412176</v>
       </c>
       <c r="D3" t="n">
         <v>10</v>
@@ -495,16 +495,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>0.8366600265340756</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8944271909999159</v>
+        <v>1.112697280528374</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -514,16 +514,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>1.032795558988645</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9574271077563381</v>
+        <v>1.154700538379252</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -533,200 +533,200 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>0.752772652709081</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5</v>
+        <v>1.618347187425374</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Komoot</t>
+          <t>Map My Run</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>0.4830458915396479</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>0.8432740427115678</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Map My Run</t>
+          <t>MyFitnessPal</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>2.097617696340303</v>
       </c>
       <c r="C8" t="n">
-        <v>1.370320319406298</v>
+        <v>2.905932629027116</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>MyFitnessPal</t>
+          <t>Nike Run Club</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>2.76457178290909</v>
+        <v>0.6749485577105528</v>
       </c>
       <c r="D9" t="n">
         <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Nike Run Club</t>
+          <t>Pacer Pedometer</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>1.060660171779821</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5676462121975467</v>
+        <v>0.9574271077563381</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Pacer</t>
+          <t>Pumatrac</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>1.290994448735806</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Pacer Pedometer &amp; Step Tracker</t>
+          <t>Runkeeper</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>1.100504934614612</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>1.649915822768611</v>
       </c>
       <c r="D12" t="n">
         <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>Polar Flow</t>
+          <t>Runtastic</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1.398411797560202</v>
       </c>
       <c r="C13" t="n">
-        <v>1.414213562373095</v>
+        <v>1.619327706865482</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Pumatrac</t>
+          <t>Samsung Health</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.5773502691896257</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Runkeeper</t>
+          <t>Sports Tracker</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8432740427115678</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>1.505545305418162</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Runtastic</t>
+          <t>Strava</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4216370213557839</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>1.286683937707919</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
         <v>10</v>
@@ -738,26 +738,26 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Samsung Health</t>
+          <t>Under Armour Record</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1.414213562373095</v>
+        <v>1.527525231651947</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Sports Tracker</t>
+          <t>Zombies, Run!</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -767,7 +767,7 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
@@ -776,77 +776,20 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Strava</t>
+          <t>Zwift</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0.3162277660168379</v>
+        <v>2.121320343559642</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>Under Armour Record</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>Zombies, Run!</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Zwift</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>1.414213562373095</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
